--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
@@ -4386,7 +4386,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
@@ -4386,7 +4386,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
@@ -5202,7 +5202,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
@@ -7164,7 +7164,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
@@ -7164,7 +7164,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
@@ -4386,7 +4386,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
@@ -4386,7 +4386,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
@@ -4386,7 +4386,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
@@ -4386,7 +4386,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
@@ -4386,7 +4386,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
@@ -4386,7 +4386,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251105_201541.xlsx
@@ -4386,7 +4386,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
